--- a/Unity/Assets/Config/Excel/Datas/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22890" windowHeight="12600"/>
+    <workbookView windowWidth="23370" windowHeight="13770"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -225,6 +225,15 @@
   </si>
   <si>
     <t>Id+Level</t>
+  </si>
+  <si>
+    <t>BuffConfigCategory</t>
+  </si>
+  <si>
+    <t>BuffConfig</t>
+  </si>
+  <si>
+    <t>BuffConfig.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8333333333333" customWidth="1"/>
@@ -1505,6 +1514,20 @@
         <v>65</v>
       </c>
     </row>
+    <row r="17" customFormat="1" spans="2:5">
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/Datas/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23370" windowHeight="13770"/>
+    <workbookView windowWidth="22080" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -234,6 +234,15 @@
   </si>
   <si>
     <t>BuffConfig.xlsx</t>
+  </si>
+  <si>
+    <t>ActionEventConfigCategory</t>
+  </si>
+  <si>
+    <t>ActionEventConfig</t>
+  </si>
+  <si>
+    <t>ActionEventConfig.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8333333333333" customWidth="1"/>
@@ -1528,6 +1537,20 @@
         <v>68</v>
       </c>
     </row>
+    <row r="18" customFormat="1" spans="2:5">
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/Datas/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/__tables__.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -243,6 +243,18 @@
   </si>
   <si>
     <t>ActionEventConfig.xlsx</t>
+  </si>
+  <si>
+    <t>TestConfigCategory</t>
+  </si>
+  <si>
+    <t>TestConfig</t>
+  </si>
+  <si>
+    <t>TestConfig.xlsx</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
 </sst>
 </file>
@@ -713,162 +725,162 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+  <cellXfs count="49">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1188,9 +1200,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <sheetPr/>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8333333333333" customWidth="1"/>
@@ -1203,7 +1215,7 @@
     <col min="12" max="12" width="33.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:13">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1244,7 +1256,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+    <row r="2" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1279,7 +1291,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="57" spans="1:12">
+    <row r="3" ht="57" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -1305,110 +1317,110 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4">
       <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5">
       <c r="B5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" s="0" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6">
       <c r="B6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" s="0" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7">
       <c r="B7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" s="0" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
-      <c r="B8" t="s">
+    <row r="8">
+      <c r="B8" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="D8" t="b">
+      <c r="D8" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
-      <c r="B9" t="s">
+    <row r="9">
+      <c r="B9" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="0" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10">
       <c r="B10" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" s="0" t="b">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1419,14 +1431,14 @@
       </c>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11">
       <c r="B11" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D11" t="b">
+      <c r="D11" s="0" t="b">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -1437,14 +1449,14 @@
       </c>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12">
       <c r="B12" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D12" t="b">
+      <c r="D12" s="0" t="b">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1455,14 +1467,14 @@
       </c>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13">
       <c r="B13" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -1472,14 +1484,14 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14">
       <c r="B14" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D14" t="b">
+      <c r="D14" s="0" t="b">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -1489,14 +1501,14 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15">
       <c r="B15" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D15" t="b">
+      <c r="D15" s="0" t="b">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -1506,49 +1518,66 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="2:6">
-      <c r="B16" t="s">
+    <row r="16">
+      <c r="B16" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="D16" t="b">
+      <c r="D16" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="0" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="2:5">
-      <c r="B17" t="s">
+    <row r="17">
+      <c r="B17" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="D17" t="b">
+      <c r="D17" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="0" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="2:5">
-      <c r="B18" t="s">
+    <row r="18">
+      <c r="B18" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="D18" t="b">
+      <c r="D18" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="0" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/Datas/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -255,6 +255,33 @@
   </si>
   <si>
     <t>Id</t>
+  </si>
+  <si>
+    <t>MonsterSpawnConfigCategory</t>
+  </si>
+  <si>
+    <t>MonsterSpawnConfig</t>
+  </si>
+  <si>
+    <t>MonsterSpawnConfig.xlsx</t>
+  </si>
+  <si>
+    <t>MonsterNumericConfigCategory</t>
+  </si>
+  <si>
+    <t>MonsterNumericConfig</t>
+  </si>
+  <si>
+    <t>MonsterNumericConfig.xlsx</t>
+  </si>
+  <si>
+    <t>PlayerNumericConfigCategory</t>
+  </si>
+  <si>
+    <t>PlayerNumericConfig</t>
+  </si>
+  <si>
+    <t>PlayerNumericConfig.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <sheetPr/>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8333333333333" customWidth="1"/>
@@ -1580,6 +1607,66 @@
         <v>75</v>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
